--- a/public/converted/upd-ut-5644-30-10-2026-fura-7-odata.xlsx
+++ b/public/converted/upd-ut-5644-30-10-2026-fura-7-odata.xlsx
@@ -504,7 +504,7 @@
           <t>КИТАЙ</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>10013160/110625/5256463/1</t>
         </is>
@@ -533,7 +533,7 @@
           <t>КИТАЙ</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>10702070/290825/5301089/1</t>
         </is>
@@ -562,7 +562,7 @@
           <t>КИТАЙ</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>10013160/010625/5237484/1</t>
         </is>
@@ -591,7 +591,7 @@
           <t>КИТАЙ</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>10702070/290825/5301089/1</t>
         </is>
@@ -620,7 +620,7 @@
           <t>КИТАЙ</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>10013160/110625/5256555/1</t>
         </is>
@@ -649,7 +649,7 @@
           <t>КИТАЙ</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>10013160/270525/5230445/1</t>
         </is>
@@ -678,7 +678,7 @@
           <t>КИТАЙ</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>10013160/010625/5237260/1</t>
         </is>
@@ -707,7 +707,7 @@
           <t>КИТАЙ</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>10013160/290525/5234599/1</t>
         </is>
@@ -736,7 +736,7 @@
           <t>КИТАЙ</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>10013160/290525/5234573/1</t>
         </is>
@@ -765,7 +765,7 @@
           <t>КИТАЙ</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>10013160/270525/5230445/2</t>
         </is>
@@ -794,7 +794,7 @@
           <t>КИТАЙ</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>10013160/290525/5234546/1</t>
         </is>
@@ -823,7 +823,7 @@
           <t>КИТАЙ</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>10702070/220425/5134929/1</t>
         </is>
@@ -852,7 +852,7 @@
           <t>КИТАЙ</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>10702070/090525/5155865/1</t>
         </is>
@@ -881,7 +881,7 @@
           <t>КИТАЙ</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>10013160/010625/5237403/1</t>
         </is>
@@ -910,7 +910,7 @@
           <t>КИТАЙ</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>10702070/130625/5200714/1</t>
         </is>
@@ -939,7 +939,7 @@
           <t>КИТАЙ</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>10702070/160625/5202418/1</t>
         </is>
@@ -968,7 +968,7 @@
           <t>КИТАЙ</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>10702070/130625/5200714/1</t>
         </is>
@@ -997,7 +997,7 @@
           <t>КИТАЙ</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>10702070/130625/5200714/1</t>
         </is>
@@ -1026,7 +1026,7 @@
           <t>КИТАЙ</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>10702070/130625/5200714/1</t>
         </is>
@@ -1055,7 +1055,7 @@
           <t>КИТАЙ</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>10702070/130625/5200714/1</t>
         </is>
@@ -1084,7 +1084,7 @@
           <t>КИТАЙ</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>10702070/160625/5202418/1</t>
         </is>
@@ -1113,7 +1113,7 @@
           <t>КИТАЙ</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>10702070/160625/5202418/1</t>
         </is>
@@ -1142,7 +1142,7 @@
           <t>КИТАЙ</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>10013160/290525/5234599/2</t>
         </is>
@@ -1171,7 +1171,7 @@
           <t>КИТАЙ</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>10013160/010625/5237260/2</t>
         </is>
@@ -1200,7 +1200,7 @@
           <t>КИТАЙ</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>10702070/140625/5200956/1</t>
         </is>
@@ -1229,7 +1229,7 @@
           <t>КИТАЙ</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>10013160/110625/5256879/2</t>
         </is>
@@ -1258,7 +1258,7 @@
           <t>КИТАЙ</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>10013160/110625/5256879/1</t>
         </is>
@@ -1287,7 +1287,7 @@
           <t>КИТАЙ</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>10013160/010625/5237420/1</t>
         </is>
@@ -1316,7 +1316,7 @@
           <t>КИТАЙ</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>10013160/270525/5230720/1</t>
         </is>
